--- a/output/Tables/2019/HIA_per_disease.xlsx
+++ b/output/Tables/2019/HIA_per_disease.xlsx
@@ -1,21 +1,95 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/2019/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3652304-176F-4A46-94C8-FC2F0A40EF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>Morbidity</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +137,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +189,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +223,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +258,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,100 +434,83 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
         <v>58496.197</v>
       </c>
       <c r="C2">
-        <v>55612.989</v>
+        <v>55612.989000000001</v>
       </c>
       <c r="D2">
-        <v>61379.951</v>
+        <v>61379.951000000001</v>
       </c>
       <c r="E2">
-        <v>604884.6580000001</v>
+        <v>604884.65800000005</v>
       </c>
       <c r="F2">
-        <v>587117.323</v>
+        <v>587117.32299999997</v>
       </c>
       <c r="G2">
-        <v>622704.426</v>
+        <v>622704.42599999998</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,41 +522,39 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>80450864508.582</v>
+        <v>80450864508.582001</v>
       </c>
       <c r="L2">
-        <v>78074500200.901</v>
+        <v>78074500200.901001</v>
       </c>
       <c r="M2">
-        <v>82820066431.078</v>
+        <v>82820066431.078003</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>40147.745</v>
+        <v>40147.745000000003</v>
       </c>
       <c r="C3">
-        <v>38394.954</v>
+        <v>38394.953999999998</v>
       </c>
       <c r="D3">
-        <v>41907.275</v>
+        <v>41907.275000000001</v>
       </c>
       <c r="E3">
         <v>35940.072</v>
       </c>
       <c r="F3">
-        <v>34538.407</v>
+        <v>34538.406999999999</v>
       </c>
       <c r="G3">
         <v>37361.195</v>
       </c>
       <c r="H3">
-        <v>2236285834.095</v>
+        <v>2236285834.0949998</v>
       </c>
       <c r="I3">
         <v>2139020016.589</v>
@@ -501,17 +566,15 @@
         <v>4780649331.573</v>
       </c>
       <c r="L3">
-        <v>4593104654.497</v>
+        <v>4593104654.4969997</v>
       </c>
       <c r="M3">
-        <v>4968855086.343</v>
+        <v>4968855086.3430004</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
         <v>31225.536</v>
@@ -520,87 +583,83 @@
         <v>29770.931</v>
       </c>
       <c r="D4">
-        <v>32738.557</v>
+        <v>32738.557000000001</v>
       </c>
       <c r="E4">
-        <v>47085.236</v>
+        <v>47085.235999999997</v>
       </c>
       <c r="F4">
-        <v>44414.475</v>
+        <v>44414.474999999999</v>
       </c>
       <c r="G4">
-        <v>49916.631</v>
+        <v>49916.631000000001</v>
       </c>
       <c r="H4">
         <v>462381324.171</v>
       </c>
       <c r="I4">
-        <v>440895317.356</v>
+        <v>440895317.35600001</v>
       </c>
       <c r="J4">
-        <v>484837826.929</v>
+        <v>484837826.92900002</v>
       </c>
       <c r="K4">
-        <v>6262145851.126</v>
+        <v>6262145851.1260004</v>
       </c>
       <c r="L4">
-        <v>5905459759.404</v>
+        <v>5905459759.4040003</v>
       </c>
       <c r="M4">
-        <v>6636403523.839</v>
+        <v>6636403523.8389997</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>6404.258</v>
+        <v>6404.2579999999998</v>
       </c>
       <c r="C5">
-        <v>6095.128</v>
+        <v>6095.1279999999997</v>
       </c>
       <c r="D5">
         <v>6721.067</v>
       </c>
       <c r="E5">
-        <v>12502.744</v>
+        <v>12502.744000000001</v>
       </c>
       <c r="F5">
-        <v>11875.522</v>
+        <v>11875.522000000001</v>
       </c>
       <c r="G5">
         <v>13142.02</v>
       </c>
       <c r="H5">
-        <v>481611509.226</v>
+        <v>481611509.22600001</v>
       </c>
       <c r="I5">
-        <v>458313512.261</v>
+        <v>458313512.26099998</v>
       </c>
       <c r="J5">
         <v>505193417.324</v>
       </c>
       <c r="K5">
-        <v>1662860969.4</v>
+        <v>1662860969.4000001</v>
       </c>
       <c r="L5">
         <v>1579278195.148</v>
       </c>
       <c r="M5">
-        <v>1747851369.462</v>
+        <v>1747851369.4619999</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
-        <v>13936.479</v>
+        <v>13936.478999999999</v>
       </c>
       <c r="C6">
         <v>13089.929</v>
@@ -609,22 +668,22 @@
         <v>14788.56</v>
       </c>
       <c r="E6">
-        <v>23252.174</v>
+        <v>23252.173999999999</v>
       </c>
       <c r="F6">
         <v>22102.18</v>
       </c>
       <c r="G6">
-        <v>24412.371</v>
+        <v>24412.370999999999</v>
       </c>
       <c r="H6">
         <v>234603634.648</v>
       </c>
       <c r="I6">
-        <v>220507915.673</v>
+        <v>220507915.67300001</v>
       </c>
       <c r="J6">
-        <v>248863397.114</v>
+        <v>248863397.11399999</v>
       </c>
       <c r="K6">
         <v>3092645316.941</v>
@@ -633,14 +692,12 @@
         <v>2938681519.855</v>
       </c>
       <c r="M6">
-        <v>3246848652.597</v>
+        <v>3246848652.5970001</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
         <v>126005.061</v>
@@ -652,10 +709,10 @@
         <v>130799.503</v>
       </c>
       <c r="E7">
-        <v>41027.609</v>
+        <v>41027.608999999997</v>
       </c>
       <c r="F7">
-        <v>38919.728</v>
+        <v>38919.728000000003</v>
       </c>
       <c r="G7">
         <v>43216.125</v>
@@ -670,96 +727,92 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>5456849853.619</v>
+        <v>5456849853.6190004</v>
       </c>
       <c r="L7">
-        <v>5174349651.046</v>
+        <v>5174349651.0459995</v>
       </c>
       <c r="M7">
-        <v>5748665005.371</v>
+        <v>5748665005.3710003</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Morbidity</t>
-        </is>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8">
         <v>217719.079</v>
       </c>
       <c r="C8">
-        <v>208641.094</v>
+        <v>208641.09400000001</v>
       </c>
       <c r="D8">
         <v>226954.962</v>
       </c>
       <c r="E8">
-        <v>159807.835</v>
+        <v>159807.83499999999</v>
       </c>
       <c r="F8">
-        <v>151850.312</v>
+        <v>151850.31200000001</v>
       </c>
       <c r="G8">
         <v>168048.342</v>
       </c>
       <c r="H8">
-        <v>3414882302.139999</v>
+        <v>3414882302.1399989</v>
       </c>
       <c r="I8">
-        <v>3258736761.879</v>
+        <v>3258736761.8790002</v>
       </c>
       <c r="J8">
-        <v>3573276711.887</v>
+        <v>3573276711.8870001</v>
       </c>
       <c r="K8">
         <v>21255151322.659</v>
       </c>
       <c r="L8">
-        <v>20190873779.95</v>
+        <v>20190873779.950001</v>
       </c>
       <c r="M8">
         <v>22348623637.612</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>276215.276</v>
+        <v>276215.27600000001</v>
       </c>
       <c r="C9">
-        <v>264254.083</v>
+        <v>264254.08299999998</v>
       </c>
       <c r="D9">
         <v>288334.913</v>
       </c>
       <c r="E9">
-        <v>764692.493</v>
+        <v>764692.49300000002</v>
       </c>
       <c r="F9">
-        <v>738967.635</v>
+        <v>738967.63500000001</v>
       </c>
       <c r="G9">
-        <v>790752.768</v>
+        <v>790752.76800000004</v>
       </c>
       <c r="H9">
-        <v>3414882302.139999</v>
+        <v>3414882302.1399989</v>
       </c>
       <c r="I9">
-        <v>3258736761.879</v>
+        <v>3258736761.8790002</v>
       </c>
       <c r="J9">
-        <v>3573276711.887</v>
+        <v>3573276711.8870001</v>
       </c>
       <c r="K9">
         <v>101706015831.241</v>
       </c>
       <c r="L9">
-        <v>98265373980.851</v>
+        <v>98265373980.850998</v>
       </c>
       <c r="M9">
         <v>105168690068.69</v>

--- a/output/Tables/2019/HIA_per_disease.xlsx
+++ b/output/Tables/2019/HIA_per_disease.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/2019/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3652304-176F-4A46-94C8-FC2F0A40EF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0523B92-F0EC-D649-A81A-7A6D5F5040BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/output/Tables/2019/HIA_per_disease.xlsx
+++ b/output/Tables/2019/HIA_per_disease.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/2019/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0523B92-F0EC-D649-A81A-7A6D5F5040BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87C244C-516C-A14E-8DAE-B222E17011AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -813,7 +813,7 @@
         <v>790752.76800000004</v>
       </c>
       <c r="H9">
-        <v>3414882302.1399989</v>
+        <v>3414882302.1399999</v>
       </c>
       <c r="I9">
         <v>3258736761.8790002</v>

--- a/output/Tables/2019/HIA_per_disease.xlsx
+++ b/output/Tables/2019/HIA_per_disease.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/2019/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87C244C-516C-A14E-8DAE-B222E17011AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E3AC8E-C1EB-B44A-A2F5-8D76EC735D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39420" yWindow="-1620" windowWidth="23220" windowHeight="14560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/output/Tables/2019/HIA_per_disease.xlsx
+++ b/output/Tables/2019/HIA_per_disease.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/2019/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E3AC8E-C1EB-B44A-A2F5-8D76EC735D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7C984F-CA0C-E948-AB76-5A2BF160B950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39420" yWindow="-1620" windowWidth="23220" windowHeight="14560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="160" yWindow="660" windowWidth="28480" windowHeight="15780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
